--- a/data/2026/cjsl/fall/sc-gjoa-strand-larsen.xlsx
+++ b/data/2026/cjsl/fall/sc-gjoa-strand-larsen.xlsx
@@ -78,7 +78,7 @@
     <col min="6" max="6" bestFit="1" customWidth="1" width="38.5"/>
     <col min="7" max="7" bestFit="1" customWidth="1" width="29.700000000000003"/>
     <col min="8" max="8" bestFit="1" customWidth="1" width="19.8"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" width="5.5"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" width="11.0"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -214,7 +214,7 @@
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Rained Out</t>
         </is>
       </c>
     </row>

--- a/data/2026/cjsl/fall/sc-gjoa-strand-larsen.xlsx
+++ b/data/2026/cjsl/fall/sc-gjoa-strand-larsen.xlsx
@@ -239,7 +239,7 @@
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2 - 4</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">

--- a/data/2026/cjsl/fall/sc-gjoa-strand-larsen.xlsx
+++ b/data/2026/cjsl/fall/sc-gjoa-strand-larsen.xlsx
@@ -76,9 +76,9 @@
     <col min="4" max="4" bestFit="1" customWidth="1" width="38.5"/>
     <col min="5" max="5" bestFit="1" customWidth="1" width="7.700000000000001"/>
     <col min="6" max="6" bestFit="1" customWidth="1" width="38.5"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" width="29.700000000000003"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" width="31.900000000000002"/>
     <col min="8" max="8" bestFit="1" customWidth="1" width="19.8"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" width="11.0"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" width="12.100000000000001"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -175,36 +175,36 @@
     </row>
     <row r="3">
       <c r="A3" s="0" t="n">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t>Saturday, September 26, 2026</t>
+          <t>Saturday, October  3, 2026</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
-          <t>09:00 EDT</t>
+          <t>10:45 EDT</t>
         </is>
       </c>
       <c r="D3" s="0" t="inlineStr">
         <is>
-          <t>ALBION SC Brooklyn B14/15 Premier - Williamsburg</t>
+          <t>SC Gjoa Strand Larsen</t>
         </is>
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2 - 4</t>
         </is>
       </c>
       <c r="F3" s="0" t="inlineStr">
         <is>
-          <t>SC Gjoa Strand Larsen</t>
+          <t>Excelsior New York Academy 2014/2015 Boys</t>
         </is>
       </c>
       <c r="G3" s="0" t="inlineStr">
         <is>
-          <t>Bushwick Inlet Park - Field 1 9v9</t>
+          <t>Dyker Turf Field A Small Sided  - A</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
@@ -214,42 +214,42 @@
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>Rained Out</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="n">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t>Saturday, October  3, 2026</t>
+          <t>Saturday, October 17, 2026</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>10:45 EDT</t>
+          <t>17:10 EDT</t>
         </is>
       </c>
       <c r="D4" s="0" t="inlineStr">
         <is>
-          <t>SC Gjoa Strand Larsen</t>
+          <t>Manhattan Kickers MKSC 2014/2015</t>
         </is>
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>2 - 4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>Excelsior New York Academy 2014/2015 Boys</t>
+          <t>SC Gjoa Strand Larsen</t>
         </is>
       </c>
       <c r="G4" s="0" t="inlineStr">
         <is>
-          <t>Dyker Turf Field A Small Sided  - A</t>
+          <t>Con Edison Field- Manhattan - 1- Manhattan</t>
         </is>
       </c>
       <c r="H4" s="0" t="inlineStr">
@@ -265,21 +265,21 @@
     </row>
     <row r="5">
       <c r="A5" s="0" t="n">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t>Saturday, October 17, 2026</t>
+          <t>Saturday, October 24, 2026</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>17:10 EDT</t>
+          <t>10:30 EDT</t>
         </is>
       </c>
       <c r="D5" s="0" t="inlineStr">
         <is>
-          <t>Manhattan Kickers MKSC 2014/2015</t>
+          <t>SC Gjoa Strand Larsen</t>
         </is>
       </c>
       <c r="E5" s="0" t="inlineStr">
@@ -289,12 +289,12 @@
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>SC Gjoa Strand Larsen</t>
+          <t>Brooklyn Italians 2014/2015 Premier</t>
         </is>
       </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
-          <t>Con Edison Field- Manhattan - 1- Manhattan</t>
+          <t>Dyker Turf Field A Small Sided  - A</t>
         </is>
       </c>
       <c r="H5" s="0" t="inlineStr">
@@ -310,16 +310,16 @@
     </row>
     <row r="6">
       <c r="A6" s="0" t="n">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t>Saturday, October 24, 2026</t>
+          <t>Saturday, October 31, 2026</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>10:30 EDT</t>
+          <t>08:00 EDT</t>
         </is>
       </c>
       <c r="D6" s="0" t="inlineStr">
@@ -334,12 +334,12 @@
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>Brooklyn Italians 2014/2015 Premier</t>
+          <t>ALBION SC Brooklyn B14/15 Premier - Williamsburg</t>
         </is>
       </c>
       <c r="G6" s="0" t="inlineStr">
         <is>
-          <t>Dyker Turf Field A Small Sided  - A</t>
+          <t>Dyker Turf Field B Small Sided  - B</t>
         </is>
       </c>
       <c r="H6" s="0" t="inlineStr">
@@ -355,21 +355,21 @@
     </row>
     <row r="7">
       <c r="A7" s="0" t="n">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t>Saturday, October 31, 2026</t>
+          <t>Saturday, November  7, 2026</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>08:00 EDT</t>
+          <t>12:45 EST</t>
         </is>
       </c>
       <c r="D7" s="0" t="inlineStr">
         <is>
-          <t>SC Gjoa Strand Larsen</t>
+          <t>Excelsior New York Academy 2014/2015 Boys</t>
         </is>
       </c>
       <c r="E7" s="0" t="inlineStr">
@@ -379,12 +379,12 @@
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>ALBION SC Brooklyn B14/15 Premier - Williamsburg</t>
+          <t>SC Gjoa Strand Larsen</t>
         </is>
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t>Dyker Turf Field B Small Sided  - B</t>
+          <t>Southern Fields - NYC Parks - 9 v 9</t>
         </is>
       </c>
       <c r="H7" s="0" t="inlineStr">
@@ -400,21 +400,21 @@
     </row>
     <row r="8">
       <c r="A8" s="0" t="n">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t>Saturday, November  7, 2026</t>
+          <t>Saturday, November 14, 2026</t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>12:45 EST</t>
+          <t>11:00 EST</t>
         </is>
       </c>
       <c r="D8" s="0" t="inlineStr">
         <is>
-          <t>Excelsior New York Academy 2014/2015 Boys</t>
+          <t>SC Gjoa Strand Larsen</t>
         </is>
       </c>
       <c r="E8" s="0" t="inlineStr">
@@ -424,12 +424,12 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>SC Gjoa Strand Larsen</t>
+          <t>Manhattan Kickers MKSC 2014/2015</t>
         </is>
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t>Southern Fields - NYC Parks - 9 v 9</t>
+          <t>Dyker Turf Field B Small Sided  - B</t>
         </is>
       </c>
       <c r="H8" s="0" t="inlineStr">
@@ -445,21 +445,21 @@
     </row>
     <row r="9">
       <c r="A9" s="0" t="n">
-        <v>296</v>
+        <v>278</v>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t>Saturday, November 14, 2026</t>
+          <t>Saturday, November 21, 2026</t>
         </is>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>11:00 EST</t>
+          <t>14:00 EST</t>
         </is>
       </c>
       <c r="D9" s="0" t="inlineStr">
         <is>
-          <t>SC Gjoa Strand Larsen</t>
+          <t>ALBION SC Brooklyn B14/15 Premier - Williamsburg</t>
         </is>
       </c>
       <c r="E9" s="0" t="inlineStr">
@@ -469,12 +469,12 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>Manhattan Kickers MKSC 2014/2015</t>
+          <t>SC Gjoa Strand Larsen</t>
         </is>
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t>Dyker Turf Field B Small Sided  - B</t>
+          <t>Bush Terminal Piers Park - Soccer 03 (Back field)</t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">
@@ -484,7 +484,7 @@
       </c>
       <c r="I9" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Rescheduled</t>
         </is>
       </c>
     </row>

--- a/data/2026/cjsl/fall/sc-gjoa-strand-larsen.xlsx
+++ b/data/2026/cjsl/fall/sc-gjoa-strand-larsen.xlsx
@@ -239,7 +239,7 @@
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2 - 3</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">

--- a/data/2026/cjsl/fall/sc-gjoa-strand-larsen.xlsx
+++ b/data/2026/cjsl/fall/sc-gjoa-strand-larsen.xlsx
@@ -284,7 +284,7 @@
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5 - 1</t>
         </is>
       </c>
       <c r="F5" s="0" t="inlineStr">
